--- a/fin_math/code/Capital Budgeting.xlsx
+++ b/fin_math/code/Capital Budgeting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sfrat\Documents\_Work Related\_My Books\Financial Math with Python\Review\Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen Fratini\Documents\_Work Related\_My Books\Financial Math with Python\Review\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584ACDF3-16B0-4952-9E82-28B10B7F65E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C269B11-D5BB-4699-B2E7-8EAC6E242FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8325" yWindow="2310" windowWidth="14820" windowHeight="10920" xr2:uid="{EAB1697F-5FC0-4B8A-A2CE-1FD59A4F4BBF}"/>
+    <workbookView xWindow="7350" yWindow="1110" windowWidth="16560" windowHeight="11175" xr2:uid="{EAB1697F-5FC0-4B8A-A2CE-1FD59A4F4BBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Acme Furniture" sheetId="1" r:id="rId1"/>
@@ -187,8 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+  <numFmts count="6">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
@@ -196,7 +195,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,6 +214,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -247,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -279,9 +285,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -297,9 +300,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -333,9 +333,6 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -380,6 +377,18 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -400,9 +409,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -440,7 +449,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -546,7 +555,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -688,7 +697,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -771,8 +780,8 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <f>NPV(0.02,B1:L1)</f>
-        <v>31923.432229326532</v>
+        <f>$B$1+NPV(B4,$C$1:$L$1)</f>
+        <v>32561.90087391308</v>
       </c>
       <c r="B4" s="5">
         <v>0.02</v>
@@ -780,8 +789,8 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <f>NPV(0.04,B1:L1)</f>
-        <v>4789.0578288004999</v>
+        <f t="shared" ref="A5:A7" si="0">$B$1+NPV(B5,$C$1:$L$1)</f>
+        <v>4980.6201419525314</v>
       </c>
       <c r="B5" s="5">
         <v>0.04</v>
@@ -789,8 +798,8 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <f>NPV(0.05,B1:L1)</f>
-        <v>-6915.4339668714993</v>
+        <f t="shared" si="0"/>
+        <v>-7261.2056652150641</v>
       </c>
       <c r="B6" s="5">
         <v>0.05</v>
@@ -798,8 +807,8 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <f>NPV(0.06,B1:L1)</f>
-        <v>-17541.147386404664</v>
+        <f t="shared" si="0"/>
+        <v>-18593.616229588981</v>
       </c>
       <c r="B7" s="5">
         <v>0.06</v>
@@ -818,8 +827,8 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <f>NPV(0.02,B1:N1)</f>
-        <v>98265.083531696859</v>
+        <f>$B$1+NPV(B10,$C$1:$N$1)</f>
+        <v>100230.38520233077</v>
       </c>
       <c r="B10" s="5">
         <v>0.02</v>
@@ -827,8 +836,8 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <f>NPV(0.04,B1:N1)</f>
-        <v>56822.796651509001</v>
+        <f t="shared" ref="A11:A14" si="1">$B$1+NPV(B11,$C$1:$N$1)</f>
+        <v>59095.70851756935</v>
       </c>
       <c r="B11" s="5">
         <v>0.04</v>
@@ -836,8 +845,8 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <f>NPV(0.06,B1:N1)</f>
-        <v>23463.513498920307</v>
+        <f t="shared" si="1"/>
+        <v>24871.324308855459</v>
       </c>
       <c r="B12" s="5">
         <v>0.06</v>
@@ -845,8 +854,8 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <f>NPV(0.07,B1:N1)</f>
-        <v>9269.2197138894699</v>
+        <f t="shared" si="1"/>
+        <v>9918.0650938617764</v>
       </c>
       <c r="B13" s="5">
         <v>7.0000000000000007E-2</v>
@@ -854,8 +863,8 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <f>NPV(0.08,B1:N1)</f>
-        <v>-3506.9504217945228</v>
+        <f t="shared" si="1"/>
+        <v>-3787.5064555380959</v>
       </c>
       <c r="B14" s="5">
         <v>0.08</v>
@@ -865,13 +874,13 @@
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <f>IRR(B1:N1)</f>
         <v>7.7149201246496935E-2</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="20"/>
+      <c r="B17" s="18"/>
     </row>
     <row r="19" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
@@ -887,43 +896,43 @@
       </c>
       <c r="C20" s="8">
         <f>C1-$B$21</f>
-        <v>14931</v>
+        <v>14578.29</v>
       </c>
       <c r="D20" s="8">
         <f>D1-$B$21</f>
-        <v>16931</v>
+        <v>16578.29</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" ref="E20:N20" si="0">E1-$B$21</f>
-        <v>18931</v>
+        <f t="shared" ref="E20:L20" si="2">E1-$B$21</f>
+        <v>18578.29</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
-        <v>20931</v>
+        <f t="shared" si="2"/>
+        <v>20578.29</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="0"/>
-        <v>22931</v>
+        <f t="shared" si="2"/>
+        <v>22578.29</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="0"/>
-        <v>24931</v>
+        <f t="shared" si="2"/>
+        <v>24578.29</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="0"/>
-        <v>26931</v>
+        <f t="shared" si="2"/>
+        <v>26578.29</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="0"/>
-        <v>28931</v>
+        <f t="shared" si="2"/>
+        <v>28578.29</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="0"/>
-        <v>30931</v>
+        <f t="shared" si="2"/>
+        <v>30578.29</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="0"/>
-        <v>32931</v>
+        <f t="shared" si="2"/>
+        <v>32578.29</v>
       </c>
       <c r="M20" s="8">
         <f>M1</f>
@@ -939,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B21" s="8">
-        <v>5069</v>
+        <v>5421.71</v>
       </c>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -954,8 +963,8 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <f>NPV(0.02,B20:N20)</f>
-        <v>53625.158633028324</v>
+        <f>$B$20+NPV(B24,$C$20:$N$20)</f>
+        <v>51529.414248137211</v>
       </c>
       <c r="B24" s="5">
         <v>0.02</v>
@@ -963,8 +972,8 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <f>NPV(0.03,B20:N20)</f>
-        <v>34429.150303085931</v>
+        <f t="shared" ref="A25:A28" si="3">$B$20+NPV(B25,$C$20:$N$20)</f>
+        <v>32453.336969619326</v>
       </c>
       <c r="B25" s="5">
         <v>0.03</v>
@@ -972,8 +981,8 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <f>NPV(0.04,B20:N20)</f>
-        <v>17289.978665402687</v>
+        <f t="shared" si="3"/>
+        <v>15120.783761682425</v>
       </c>
       <c r="B26" s="5">
         <v>0.04</v>
@@ -981,8 +990,8 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <f>NPV(0.05,B20:N20)</f>
-        <v>1971.444982003512</v>
+        <f t="shared" si="3"/>
+        <v>-653.51589576914557</v>
       </c>
       <c r="B27" s="5">
         <v>0.05</v>
@@ -990,21 +999,18 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <f>NPV(0.06,B20:N20)</f>
-        <v>-11732.978259212809</v>
+        <f t="shared" si="3"/>
+        <v>-15032.933258670062</v>
       </c>
       <c r="B28" s="5">
         <v>0.06</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="19"/>
+      <c r="B30" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A4:A7" formulaRange="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1021,7 +1027,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C1" s="1">
@@ -1089,348 +1095,348 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="40">
+      <c r="C2" s="39"/>
+      <c r="D2" s="37">
         <v>20000</v>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="37">
         <v>22000</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="37">
         <v>24000</v>
       </c>
-      <c r="G2" s="40">
+      <c r="G2" s="37">
         <v>26000</v>
       </c>
-      <c r="H2" s="40">
+      <c r="H2" s="37">
         <v>28000</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="37">
         <v>30000</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="37">
         <v>32000</v>
       </c>
-      <c r="K2" s="40">
+      <c r="K2" s="37">
         <v>34000</v>
       </c>
-      <c r="L2" s="40">
+      <c r="L2" s="37">
         <v>36000</v>
       </c>
-      <c r="M2" s="40">
+      <c r="M2" s="37">
         <v>38000</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="37">
         <v>41000</v>
       </c>
-      <c r="O2" s="40">
+      <c r="O2" s="37">
         <v>44000</v>
       </c>
-      <c r="P2" s="42">
+      <c r="P2" s="39">
         <v>0</v>
       </c>
-      <c r="Q2" s="42">
+      <c r="Q2" s="39">
         <v>0</v>
       </c>
-      <c r="R2" s="42">
+      <c r="R2" s="39">
         <v>0</v>
       </c>
-      <c r="S2" s="42">
+      <c r="S2" s="39">
         <v>0</v>
       </c>
-      <c r="T2" s="42">
+      <c r="T2" s="39">
         <v>0</v>
       </c>
-      <c r="U2" s="42">
+      <c r="U2" s="39">
         <v>0</v>
       </c>
-      <c r="V2" s="42">
+      <c r="V2" s="39">
         <v>0</v>
       </c>
-      <c r="W2" s="42">
+      <c r="W2" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="37">
         <v>-225000</v>
       </c>
-      <c r="D3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="E3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="F3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="G3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="H3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="I3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="J3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="K3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="L3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="M3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="N3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="O3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="P3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="Q3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="R3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="S3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="T3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="U3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="V3" s="42">
-        <v>-2566</v>
-      </c>
-      <c r="W3" s="42">
-        <v>-2566</v>
+      <c r="D3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="E3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="F3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="G3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="H3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="I3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="J3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="K3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="L3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="M3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="N3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="O3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="P3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="Q3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="R3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="S3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="T3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="U3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="V3" s="39">
+        <v>-2912.29</v>
+      </c>
+      <c r="W3" s="39">
+        <v>-2912.29</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C4" s="39">
         <f>SUM(C2:C3)</f>
         <v>-225000</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="39">
         <f t="shared" ref="D4:W4" si="0">SUM(D2:D3)</f>
-        <v>17434</v>
-      </c>
-      <c r="E4" s="42">
-        <f t="shared" si="0"/>
-        <v>19434</v>
-      </c>
-      <c r="F4" s="42">
-        <f t="shared" si="0"/>
-        <v>21434</v>
-      </c>
-      <c r="G4" s="42">
-        <f t="shared" si="0"/>
-        <v>23434</v>
-      </c>
-      <c r="H4" s="42">
-        <f t="shared" si="0"/>
-        <v>25434</v>
-      </c>
-      <c r="I4" s="42">
-        <f t="shared" si="0"/>
-        <v>27434</v>
-      </c>
-      <c r="J4" s="42">
-        <f t="shared" si="0"/>
-        <v>29434</v>
-      </c>
-      <c r="K4" s="42">
-        <f t="shared" si="0"/>
-        <v>31434</v>
-      </c>
-      <c r="L4" s="42">
-        <f t="shared" si="0"/>
-        <v>33434</v>
-      </c>
-      <c r="M4" s="42">
-        <f t="shared" si="0"/>
-        <v>35434</v>
-      </c>
-      <c r="N4" s="42">
-        <f t="shared" si="0"/>
-        <v>38434</v>
-      </c>
-      <c r="O4" s="42">
-        <f t="shared" si="0"/>
-        <v>41434</v>
-      </c>
-      <c r="P4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="Q4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="R4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="S4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="T4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="U4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="V4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
-      </c>
-      <c r="W4" s="42">
-        <f t="shared" si="0"/>
-        <v>-2566</v>
+        <v>17087.71</v>
+      </c>
+      <c r="E4" s="39">
+        <f t="shared" si="0"/>
+        <v>19087.71</v>
+      </c>
+      <c r="F4" s="39">
+        <f t="shared" si="0"/>
+        <v>21087.71</v>
+      </c>
+      <c r="G4" s="39">
+        <f t="shared" si="0"/>
+        <v>23087.71</v>
+      </c>
+      <c r="H4" s="39">
+        <f t="shared" si="0"/>
+        <v>25087.71</v>
+      </c>
+      <c r="I4" s="39">
+        <f t="shared" si="0"/>
+        <v>27087.71</v>
+      </c>
+      <c r="J4" s="39">
+        <f t="shared" si="0"/>
+        <v>29087.71</v>
+      </c>
+      <c r="K4" s="39">
+        <f t="shared" si="0"/>
+        <v>31087.71</v>
+      </c>
+      <c r="L4" s="39">
+        <f t="shared" si="0"/>
+        <v>33087.71</v>
+      </c>
+      <c r="M4" s="39">
+        <f t="shared" si="0"/>
+        <v>35087.71</v>
+      </c>
+      <c r="N4" s="39">
+        <f t="shared" si="0"/>
+        <v>38087.71</v>
+      </c>
+      <c r="O4" s="39">
+        <f t="shared" si="0"/>
+        <v>41087.71</v>
+      </c>
+      <c r="P4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="Q4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="R4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="S4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="T4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="U4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="V4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
+      </c>
+      <c r="W4" s="39">
+        <f t="shared" si="0"/>
+        <v>-2912.29</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="45" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
-        <f>NPV(B9,$C$4:$W$4)</f>
-        <v>57130.007098131922</v>
+      <c r="A9" s="40">
+        <f>$C$4+NPV(B9,$D$4:$W$4)</f>
+        <v>52610.269387194014</v>
       </c>
       <c r="B9" s="1">
         <v>0.02</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
-        <f t="shared" ref="A10:A21" si="1">NPV(B10,$C$4:$W$4)</f>
-        <v>48010.025661039232</v>
+      <c r="A10" s="40">
+        <f t="shared" ref="A10:A21" si="1">$C$4+NPV(B10,$D$4:$W$4)</f>
+        <v>43811.90529466857</v>
       </c>
       <c r="B10" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
-        <f t="shared" si="1"/>
-        <v>39345.652912491612</v>
+      <c r="A11" s="40">
+        <f t="shared" si="1"/>
+        <v>35374.101730439201</v>
       </c>
       <c r="B11" s="1">
         <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
-        <f t="shared" si="1"/>
-        <v>31113.472319763805</v>
+      <c r="A12" s="40">
+        <f t="shared" si="1"/>
+        <v>27280.830711522489</v>
       </c>
       <c r="B12" s="1">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
-        <f t="shared" si="1"/>
-        <v>23291.27991959835</v>
+      <c r="A13" s="40">
+        <f t="shared" si="1"/>
+        <v>19516.737006383482</v>
       </c>
       <c r="B13" s="1">
         <v>0.04</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
-        <f t="shared" si="1"/>
-        <v>15858.028207577408</v>
+      <c r="A14" s="40">
+        <f t="shared" si="1"/>
+        <v>12067.121163144475</v>
       </c>
       <c r="B14" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
-        <f t="shared" si="1"/>
-        <v>8793.7712839846172</v>
+      <c r="A15" s="40">
+        <f t="shared" si="1"/>
+        <v>4917.9210286657326</v>
       </c>
       <c r="B15" s="1">
         <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
-        <f t="shared" si="1"/>
-        <v>2079.6114765904472</v>
+      <c r="A16" s="40">
+        <f t="shared" si="1"/>
+        <v>-1944.3078429029556</v>
       </c>
       <c r="B16" s="1">
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
-        <f t="shared" si="1"/>
-        <v>-4302.3523943234795</v>
+      <c r="A17" s="40">
+        <f t="shared" si="1"/>
+        <v>-8532.4125567598967</v>
       </c>
       <c r="B17" s="1">
         <v>0.06</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
-        <f t="shared" si="1"/>
-        <v>-10369.074989237455</v>
+      <c r="A18" s="40">
+        <f t="shared" si="1"/>
+        <v>-14858.663738227187</v>
       </c>
       <c r="B18" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
-        <f t="shared" si="1"/>
-        <v>-16136.612579563285</v>
+      <c r="A19" s="40">
+        <f t="shared" si="1"/>
+        <v>-20934.776653212466</v>
       </c>
       <c r="B19" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
-        <f t="shared" si="1"/>
-        <v>-21620.169284695137</v>
+      <c r="A20" s="40">
+        <f t="shared" si="1"/>
+        <v>-26771.9323938218</v>
       </c>
       <c r="B20" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="43">
-        <f t="shared" si="1"/>
-        <v>-26834.141391715682</v>
+      <c r="A21" s="40">
+        <f t="shared" si="1"/>
+        <v>-32380.798968778603</v>
       </c>
       <c r="B21" s="1">
         <v>0.08</v>
@@ -1530,96 +1536,97 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <f>NPV(0.005,A1:U1)</f>
-        <v>97678.02053116243</v>
-      </c>
-      <c r="B4" s="11">
+        <f>$A$1+NPV(B4,$B$1:$U$1)</f>
+        <v>98166.410633818246</v>
+      </c>
+      <c r="B4" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <f>NPV(0.0075,A1:U1)</f>
-        <v>82930.675948433345</v>
-      </c>
-      <c r="B5" s="11">
+        <f t="shared" ref="A5:A13" si="0">$A$1+NPV(B5,$B$1:$U$1)</f>
+        <v>83552.656018046546</v>
+      </c>
+      <c r="B5" s="1">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>NPV(0.01,A1:U1)</f>
-        <v>68757.606960409568</v>
-      </c>
-      <c r="B6" s="11">
+        <f t="shared" si="0"/>
+        <v>69445.183030013693</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.01</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f>NPV(0.0125,A1:U1)</f>
-        <v>55134.236904583995</v>
-      </c>
-      <c r="B7" s="11">
+        <f t="shared" si="0"/>
+        <v>55823.414865891216</v>
+      </c>
+      <c r="B7" s="1">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f>NPV(0.015,A1:U1)</f>
-        <v>42037.145320293239</v>
-      </c>
-      <c r="B8" s="11">
+        <f t="shared" si="0"/>
+        <v>42667.70250009757</v>
+      </c>
+      <c r="B8" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f>NPV(0.0175,A1:U1)</f>
-        <v>29444.009265208912</v>
-      </c>
-      <c r="B9" s="11">
+        <f t="shared" si="0"/>
+        <v>29959.279427350033</v>
+      </c>
+      <c r="B9" s="1">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f>NPV(0.02,A1:U1)</f>
-        <v>17333.547804047481</v>
-      </c>
-      <c r="B10" s="11">
+        <f t="shared" si="0"/>
+        <v>17680.218760128366</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f>NPV(0.0225,A1:U1)</f>
-        <v>5685.4694884060009</v>
-      </c>
-      <c r="B11" s="11">
+        <f t="shared" si="0"/>
+        <v>5813.3925518949982</v>
+      </c>
+      <c r="B11" s="1">
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <f>NPV(0.025,A1:U1)</f>
-        <v>-5519.5773424754016</v>
-      </c>
-      <c r="B12" s="11">
+      <c r="A12" s="42">
+        <f t="shared" si="0"/>
+        <v>-5657.5667760372744</v>
+      </c>
+      <c r="B12" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f>NPV(0.0275,A1:U1)</f>
-        <v>-16300.051600094019</v>
-      </c>
-      <c r="B13" s="11">
+      <c r="A13" s="42">
+        <f t="shared" si="0"/>
+        <v>-16748.303019096551</v>
+      </c>
+      <c r="B13" s="1">
         <v>2.75E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1628,7 +1635,8 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -1637,253 +1645,253 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="17">
+      <c r="D1" s="5">
         <v>0</v>
       </c>
-      <c r="E1" s="17">
+      <c r="E1" s="5">
         <v>1</v>
       </c>
-      <c r="F1" s="17">
+      <c r="F1" s="5">
         <v>2</v>
       </c>
-      <c r="G1" s="17">
+      <c r="G1" s="5">
         <v>3</v>
       </c>
-      <c r="H1" s="17">
+      <c r="H1" s="5">
         <v>4</v>
       </c>
-      <c r="I1" s="17">
+      <c r="I1" s="5">
         <v>5</v>
       </c>
-      <c r="J1" s="17">
+      <c r="J1" s="5">
         <v>6</v>
       </c>
-      <c r="K1" s="17">
+      <c r="K1" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25" t="s">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="27">
+      <c r="D2" s="26"/>
+      <c r="E2" s="25">
         <v>7500</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="25">
         <v>10000</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="25">
         <v>12500</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="25">
         <v>15000</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="25">
         <v>15000</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="25">
         <v>17500</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="25">
         <v>20000</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="25">
         <v>-70000</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25">
         <v>-10000</v>
       </c>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="25">
         <v>-70000</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="25">
         <v>7500</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="25">
         <v>10000</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="25">
         <v>12500</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="25">
         <f>SUM(H2:H3)</f>
         <v>5000</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="25">
         <v>15000</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="25">
         <v>17500</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="25">
         <v>20000</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
-        <f>NPV(B7,$D$4:$K$4)</f>
-        <v>9705.4413811827872</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="25">
+        <f>$D$4+NPV(B7,$E$4:$K$4)</f>
+        <v>9899.5502088064386</v>
+      </c>
+      <c r="B7" s="11">
         <v>0.02</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
-        <f t="shared" ref="A8:A12" si="0">NPV(B8,$D$4:$K$4)</f>
-        <v>6258.4028694002109</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="25">
+        <f t="shared" ref="A8:A12" si="0">$D$4+NPV(B8,$E$4:$K$4)</f>
+        <v>6446.1549554822268</v>
+      </c>
+      <c r="B8" s="11">
         <v>0.03</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
-        <f t="shared" si="0"/>
-        <v>3078.2145153462734</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="25">
+        <f t="shared" si="0"/>
+        <v>3201.3430959601246</v>
+      </c>
+      <c r="B9" s="11">
         <v>0.04</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
-        <f>NPV(B10,$D$4:$K$4)</f>
-        <v>142.78364172456349</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="25">
+        <f t="shared" si="0"/>
+        <v>149.9228238108044</v>
+      </c>
+      <c r="B10" s="11">
         <v>0.05</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
-        <f t="shared" si="0"/>
-        <v>-2567.9530419986836</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="43">
+        <f t="shared" si="0"/>
+        <v>-2722.0302245186176</v>
+      </c>
+      <c r="B11" s="11">
         <v>0.06</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
-        <f t="shared" si="0"/>
-        <v>-5072.2345371647461</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="43">
+        <f t="shared" si="0"/>
+        <v>-5427.2909547662784</v>
+      </c>
+      <c r="B12" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1983,12 +1991,12 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <f>NPV(C6,D1:N1)</f>
-        <v>18534.070769394792</v>
+        <f>$D$1+NPV(C6,$E$1:$N$1)</f>
+        <v>18904.752184782643</v>
       </c>
       <c r="B6" s="6">
-        <f>NPV(C6,D2:N2)</f>
-        <v>144789.9045311168</v>
+        <f>$D$2+NPV(C6,$E$2:$N$2)</f>
+        <v>147685.70262173912</v>
       </c>
       <c r="C6" s="5">
         <v>0.02</v>
@@ -1996,12 +2004,12 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <f>NPV(C7,D1:N1)</f>
-        <v>604.07735734712332</v>
+        <f t="shared" ref="A7:A15" si="0">$D$1+NPV(C7,$E$1:$N$1)</f>
+        <v>619.17929128068499</v>
       </c>
       <c r="B7" s="6">
-        <f>NPV(C7,D2:N2)</f>
-        <v>122676.11234101163</v>
+        <f t="shared" ref="B7:B15" si="1">$D$2+NPV(C7,$E$2:$N$2)</f>
+        <v>125743.01514953689</v>
       </c>
       <c r="C7" s="5">
         <v>2.5000000000000001E-2</v>
@@ -2009,12 +2017,12 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <f>NPV(C8,D1:N1)</f>
-        <v>-16452.339993312784</v>
+        <f t="shared" si="0"/>
+        <v>-16945.910193112097</v>
       </c>
       <c r="B8" s="6">
-        <f>NPV(C8,D2:N2)</f>
-        <v>101616.41530899554</v>
+        <f t="shared" si="1"/>
+        <v>104664.90776826523</v>
       </c>
       <c r="C8" s="5">
         <v>0.03</v>
@@ -2022,12 +2030,12 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <f>NPV(C9,D1:N1)</f>
-        <v>-32680.600637332653</v>
+        <f t="shared" si="0"/>
+        <v>-33824.421659639222</v>
       </c>
       <c r="B9" s="6">
-        <f>NPV(C9,D2:N2)</f>
-        <v>81556.226095104255</v>
+        <f t="shared" si="1"/>
+        <v>84410.694008432794</v>
       </c>
       <c r="C9" s="5">
         <v>3.5000000000000003E-2</v>
@@ -2035,12 +2043,12 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <f>NPV(C10,D1:N1)</f>
-        <v>-48123.509274152537</v>
+        <f t="shared" si="0"/>
+        <v>-50048.449645118671</v>
       </c>
       <c r="B10" s="6">
-        <f>NPV(C10,D2:N2)</f>
-        <v>62444.096563324609</v>
+        <f t="shared" si="1"/>
+        <v>64941.860425857594</v>
       </c>
       <c r="C10" s="5">
         <v>0.04</v>
@@ -2048,12 +2056,12 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <f>NPV(C11,D1:N1)</f>
-        <v>-62821.420892151291</v>
+        <f t="shared" si="0"/>
+        <v>-65648.38483229815</v>
       </c>
       <c r="B11" s="6">
-        <f>NPV(C11,D2:N2)</f>
-        <v>44231.519809801277</v>
+        <f t="shared" si="1"/>
+        <v>46221.938201242243</v>
       </c>
       <c r="C11" s="5">
         <v>4.4999999999999998E-2</v>
@@ -2061,12 +2069,12 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <f>NPV(C12,D1:N1)</f>
-        <v>-76812.394440988253</v>
+        <f t="shared" si="0"/>
+        <v>-80653.014163037529</v>
       </c>
       <c r="B12" s="6">
-        <f>NPV(C12,D2:N2)</f>
-        <v>26872.74571843326</v>
+        <f t="shared" si="1"/>
+        <v>28216.383004354779</v>
       </c>
       <c r="C12" s="5">
         <v>0.05</v>
@@ -2074,12 +2082,12 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <f>NPV(C13,D1:N1)</f>
-        <v>-90132.336058868692</v>
+        <f t="shared" si="0"/>
+        <v>-95089.614542106399</v>
       </c>
       <c r="B13" s="6">
-        <f>NPV(C13,D2:N2)</f>
-        <v>10324.609051632486</v>
+        <f t="shared" si="1"/>
+        <v>10892.462549472344</v>
       </c>
       <c r="C13" s="5">
         <v>5.5E-2</v>
@@ -2087,12 +2095,12 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <f>NPV(C14,D1:N1)</f>
-        <v>-102815.13261695513</v>
+        <f t="shared" si="0"/>
+        <v>-108984.04057397234</v>
       </c>
       <c r="B14" s="6">
-        <f>NPV(C14,D2:N2)</f>
-        <v>-5453.6308384592694</v>
+        <f t="shared" si="1"/>
+        <v>-5780.8486887668259</v>
       </c>
       <c r="C14" s="5">
         <v>0.06</v>
@@ -2100,12 +2108,12 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <f>NPV(C15,D1:N1)</f>
-        <v>-114892.77628381866</v>
+        <f t="shared" si="0"/>
+        <v>-122360.80674226675</v>
       </c>
       <c r="B15" s="6">
-        <f>NPV(C15,D2:N2)</f>
-        <v>-20500.439521803004</v>
+        <f t="shared" si="1"/>
+        <v>-21832.968090720242</v>
       </c>
       <c r="C15" s="5">
         <v>6.5000000000000002E-2</v>
@@ -2121,335 +2129,335 @@
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15.28515625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="10" style="12" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="2" width="15.28515625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="10" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="14">
+      <c r="D1" s="13">
         <v>-155000</v>
       </c>
-      <c r="E1" s="14">
+      <c r="E1" s="13">
         <v>20000</v>
       </c>
-      <c r="F1" s="14">
+      <c r="F1" s="13">
         <v>20000</v>
       </c>
-      <c r="G1" s="14">
+      <c r="G1" s="13">
         <v>30000</v>
       </c>
-      <c r="H1" s="14">
+      <c r="H1" s="13">
         <v>40000</v>
       </c>
-      <c r="I1" s="14">
+      <c r="I1" s="13">
         <v>30000</v>
       </c>
-      <c r="J1" s="14">
+      <c r="J1" s="13">
         <v>30000</v>
       </c>
-      <c r="K1" s="14">
+      <c r="K1" s="13">
         <v>25000</v>
       </c>
-      <c r="L1" s="14">
+      <c r="L1" s="13">
         <v>5000</v>
       </c>
-      <c r="N1" s="14">
+      <c r="N1" s="13">
         <f>SUM(E1:L1)</f>
         <v>200000</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>-155000</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>50000</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>10000</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>20000</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <v>20000</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>20000</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>30000</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>25000</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>25000</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="13">
         <f>SUM(E2:L2)</f>
         <v>200000</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C3" s="15"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="N3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="N3" s="13"/>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="14"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
-        <f>NPV(C6,$D$1:$L$1)</f>
-        <v>28330.615609086421</v>
-      </c>
-      <c r="B6" s="18">
-        <f>NPV(C6,$D$2:$L$2)</f>
-        <v>28244.776739483332</v>
-      </c>
-      <c r="C6" s="17">
+      <c r="A6" s="16">
+        <f>$D$1+NPV(C6,$E$1:$L$1)</f>
+        <v>28897.227921268146</v>
+      </c>
+      <c r="B6" s="16">
+        <f>$D$2+NPV(C6,$E$2:$L$2)</f>
+        <v>28809.672274273005</v>
+      </c>
+      <c r="C6" s="5">
         <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
-        <f t="shared" ref="A7:A16" si="0">NPV(C7,$D$1:$L$1)</f>
-        <v>24550.623905990564</v>
-      </c>
-      <c r="B7" s="18">
-        <f t="shared" ref="B7:B16" si="1">NPV(C7,$D$2:$L$2)</f>
-        <v>24474.068058159824</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="A7" s="16">
+        <f t="shared" ref="A7:A16" si="0">$D$2+NPV(C7,$E$1:$L$1)</f>
+        <v>25164.389503640356</v>
+      </c>
+      <c r="B7" s="16">
+        <f t="shared" ref="B7:B16" si="1">$D$2+NPV(C7,$E$2:$L$2)</f>
+        <v>25085.919759613811</v>
+      </c>
+      <c r="C7" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
-        <f t="shared" si="0"/>
-        <v>20912.86484974837</v>
-      </c>
-      <c r="B8" s="18">
-        <f t="shared" si="1"/>
-        <v>20855.771443425234</v>
-      </c>
-      <c r="C8" s="17">
+      <c r="A8" s="16">
+        <f t="shared" si="0"/>
+        <v>21540.250795240834</v>
+      </c>
+      <c r="B8" s="16">
+        <f t="shared" si="1"/>
+        <v>21481.444586728001</v>
+      </c>
+      <c r="C8" s="5">
         <v>0.03</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
-        <f t="shared" si="0"/>
-        <v>17411.49943580796</v>
-      </c>
-      <c r="B9" s="18">
-        <f t="shared" si="1"/>
-        <v>17383.120776678355</v>
-      </c>
-      <c r="C9" s="17">
+      <c r="A9" s="16">
+        <f t="shared" si="0"/>
+        <v>18020.901916061237</v>
+      </c>
+      <c r="B9" s="16">
+        <f t="shared" si="1"/>
+        <v>17991.530003862106</v>
+      </c>
+      <c r="C9" s="5">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
-        <f t="shared" si="0"/>
-        <v>14040.958867487621</v>
-      </c>
-      <c r="B10" s="18">
-        <f t="shared" si="1"/>
-        <v>14049.687080101903</v>
-      </c>
-      <c r="C10" s="17">
+      <c r="A10" s="16">
+        <f t="shared" si="0"/>
+        <v>14602.597222187149</v>
+      </c>
+      <c r="B10" s="16">
+        <f t="shared" si="1"/>
+        <v>14611.674563306005</v>
+      </c>
+      <c r="C10" s="5">
         <v>0.04</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
-        <f t="shared" si="0"/>
-        <v>10795.930613642033</v>
-      </c>
-      <c r="B11" s="18">
-        <f t="shared" si="1"/>
-        <v>10849.359915914752</v>
-      </c>
-      <c r="C11" s="17">
+      <c r="A11" s="16">
+        <f t="shared" si="0"/>
+        <v>11281.747491255956</v>
+      </c>
+      <c r="B11" s="16">
+        <f t="shared" si="1"/>
+        <v>11337.581112130923</v>
+      </c>
+      <c r="C11" s="5">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
-        <f t="shared" si="0"/>
-        <v>7671.3452580463481</v>
-      </c>
-      <c r="B12" s="18">
-        <f t="shared" si="1"/>
-        <v>7776.3299071747451</v>
-      </c>
-      <c r="C12" s="17">
+      <c r="A12" s="16">
+        <f t="shared" si="0"/>
+        <v>8054.912520948681</v>
+      </c>
+      <c r="B12" s="16">
+        <f t="shared" si="1"/>
+        <v>8165.1464025334863</v>
+      </c>
+      <c r="C12" s="5">
         <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
-        <f t="shared" si="0"/>
-        <v>4662.3640915657124</v>
-      </c>
-      <c r="B13" s="18">
-        <f t="shared" si="1"/>
-        <v>4825.0723069810074</v>
-      </c>
-      <c r="C13" s="17">
+      <c r="A13" s="16">
+        <f t="shared" si="0"/>
+        <v>4918.7941166018427</v>
+      </c>
+      <c r="B13" s="16">
+        <f t="shared" si="1"/>
+        <v>5090.4512838649971</v>
+      </c>
+      <c r="C13" s="5">
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
-        <f t="shared" si="0"/>
-        <v>1764.3674014302915</v>
-      </c>
-      <c r="B14" s="18">
-        <f t="shared" si="1"/>
-        <v>1990.3315480368342</v>
-      </c>
-      <c r="C14" s="17">
+      <c r="A14" s="16">
+        <f t="shared" si="0"/>
+        <v>1870.2294455161027</v>
+      </c>
+      <c r="B14" s="16">
+        <f t="shared" si="1"/>
+        <v>2109.7514409190335</v>
+      </c>
+      <c r="C14" s="5">
         <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
-        <f>NPV(C15,$D$1:$L$1)</f>
-        <v>-1027.0565850236687</v>
-      </c>
-      <c r="B15" s="18">
-        <f>NPV(C15,$D$2:$L$2)</f>
-        <v>-732.893290718456</v>
-      </c>
-      <c r="C15" s="17">
+      <c r="A15" s="16">
+        <f t="shared" si="0"/>
+        <v>-1093.8152630501718</v>
+      </c>
+      <c r="B15" s="16">
+        <f t="shared" si="1"/>
+        <v>-780.53135461517377</v>
+      </c>
+      <c r="C15" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
-        <f t="shared" si="0"/>
-        <v>-3716.1221419786084</v>
-      </c>
-      <c r="B16" s="18">
-        <f t="shared" si="1"/>
-        <v>-3349.3621593215412</v>
-      </c>
-      <c r="C16" s="17">
+      <c r="A16" s="16">
+        <f t="shared" si="0"/>
+        <v>-3976.2506919171137</v>
+      </c>
+      <c r="B16" s="16">
+        <f t="shared" si="1"/>
+        <v>-3583.8175104740658</v>
+      </c>
+      <c r="C16" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="17"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <f>IRR(D1:L1)</f>
         <v>6.3138516712945902E-2</v>
       </c>
-      <c r="C18" s="17"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <f>IRR(D2:L2)</f>
         <v>6.363454958751058E-2</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="21"/>
-      <c r="C20" s="17"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <f>MIRR(D1:L1,0.025,0.015)</f>
         <v>3.9608939517476127E-2</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <f>MIRR(D2:L2,0.025,0.015)</f>
         <v>3.9549952625891116E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="21"/>
+      <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="21"/>
+      <c r="B25" s="19"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="19">
         <f>MIRR(D1:L1,0.06,0.08)</f>
         <v>7.1488275470998675E-2</v>
       </c>
-      <c r="C26" s="13"/>
+      <c r="C26" s="12"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="19">
         <f>MIRR(D2:L2,0.06,0.08)</f>
         <v>7.200753000613358E-2</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2472,7 +2480,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="4">
@@ -2495,15 +2503,15 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="20">
         <f>IRR($C$1:$H$1,0.05)</f>
         <v>5.0698827466135299E-2</v>
       </c>
@@ -2512,7 +2520,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <f>IRR($C$1:$H$1,0.8)</f>
         <v>0.82425405475180735</v>
       </c>
@@ -2521,13 +2529,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
+      <c r="A6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
+      <c r="A7" s="20"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
+      <c r="A8" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2539,15 +2547,15 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="36"/>
-    <col min="2" max="2" width="10.7109375" style="36" customWidth="1"/>
-    <col min="3" max="3" width="15" style="36" customWidth="1"/>
-    <col min="4" max="9" width="9.85546875" style="36" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="36"/>
+    <col min="1" max="1" width="9.140625" style="33"/>
+    <col min="2" max="2" width="10.7109375" style="33" customWidth="1"/>
+    <col min="3" max="3" width="15" style="33" customWidth="1"/>
+    <col min="4" max="9" width="9.85546875" style="33" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="34" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="5">
@@ -2570,25 +2578,25 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="35">
         <v>-25000</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="35">
         <v>-5000</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="35">
         <v>5000</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="35">
         <v>20000</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="35">
         <v>20000</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I2" s="35">
         <v>20000</v>
       </c>
     </row>
@@ -2596,7 +2604,7 @@
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <f>IRR(D2:I2)</f>
         <v>0.23988970216065275</v>
       </c>
@@ -2605,7 +2613,7 @@
       <c r="A5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <f>MIRR(D2:I2,0.05,0.04)</f>
         <v>0.17989007473261553</v>
       </c>
@@ -2620,404 +2628,404 @@
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="13" customWidth="1"/>
-    <col min="3" max="4" width="9.85546875" style="13" customWidth="1"/>
-    <col min="5" max="10" width="8.7109375" style="13" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="21.28515625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="12" customWidth="1"/>
+    <col min="3" max="4" width="9.85546875" style="12" customWidth="1"/>
+    <col min="5" max="10" width="8.7109375" style="12" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>0</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>1</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>2</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>3</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>4</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>5</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>6</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <v>7</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="31">
         <v>-155000</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="31">
         <v>20000</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="31">
         <v>20000</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="31">
         <v>30000</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="31">
         <v>40000</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="31">
         <v>30000</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="31">
         <v>30000</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="31">
         <v>25000</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="31">
         <v>5000</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="31">
         <v>-155000</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="31">
         <f>C4*(1+$B$2)^-C3</f>
         <v>19512.195121951223</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="31">
         <f t="shared" ref="D5:J5" si="0">D4*(1+$B$2)^-D3</f>
         <v>19036.287923854848</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="31">
         <f t="shared" si="0"/>
         <v>27857.982327592465</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="31">
         <f t="shared" si="0"/>
         <v>36238.0257919902</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="31">
         <f t="shared" si="0"/>
         <v>26515.628628285514</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="31">
         <f t="shared" si="0"/>
         <v>25868.905978815139</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="31">
         <f t="shared" si="0"/>
         <v>21031.630877085478</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="31">
         <f t="shared" si="0"/>
         <v>4103.7328540654598</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="31">
         <f>SUM($B$5:B5)</f>
         <v>-155000</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="31">
         <f>SUM($B$5:C5)</f>
         <v>-135487.80487804877</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="31">
         <f>SUM($B$5:D5)</f>
         <v>-116451.51695419392</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="31">
         <f>SUM($B$5:E5)</f>
         <v>-88593.534626601468</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="31">
         <f>SUM($B$5:F5)</f>
         <v>-52355.508834611268</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="31">
         <f>SUM($B$5:G5)</f>
         <v>-25839.880206325754</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="31">
         <f>SUM($B$5:H5)</f>
         <v>29.025772489385417</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="31">
         <f>SUM($B$5:I5)</f>
         <v>21060.656649574863</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="31">
         <f>SUM($B$5:J5)</f>
         <v>25164.389503640323</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <f>NPV(0.025,C4:J4)</f>
         <v>180164.38950364036</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>155000</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="41">
         <f>B7/B8</f>
         <v>1.1623509000234862</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-    </row>
-    <row r="10" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+    </row>
+    <row r="10" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>0</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <v>1</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>2</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>3</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>4</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>5</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>6</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>7</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="31">
         <v>-155000</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="31">
         <v>50000</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="31">
         <v>10000</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="31">
         <v>20000</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="31">
         <v>20000</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="31">
         <v>20000</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="31">
         <v>30000</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="31">
         <v>25000</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="31">
         <v>25000</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="31">
         <v>-155000</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="31">
         <f>C14*(1+$B$12)^-C13</f>
         <v>48780.487804878052</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="31">
         <f t="shared" ref="D15:J15" si="1">D14*(1+$B$12)^-D13</f>
         <v>9518.1439619274242</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="31">
         <f t="shared" si="1"/>
         <v>18571.988218394978</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="31">
         <f t="shared" si="1"/>
         <v>18119.0128959951</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="31">
         <f t="shared" si="1"/>
         <v>17677.085752190342</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="31">
         <f t="shared" si="1"/>
         <v>25868.905978815139</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="31">
         <f t="shared" si="1"/>
         <v>21031.630877085478</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="31">
         <f t="shared" si="1"/>
         <v>20518.664270327296</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="31">
         <f>SUM($B$15:B15)</f>
         <v>-155000</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="31">
         <f>SUM($B$15:C15)</f>
         <v>-106219.51219512195</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="31">
         <f>SUM($B$15:D15)</f>
         <v>-96701.368233194517</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="31">
         <f>SUM($B$15:E15)</f>
         <v>-78129.380014799535</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="31">
         <f>SUM($B$15:F15)</f>
         <v>-60010.367118804439</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="31">
         <f>SUM($B$15:G15)</f>
         <v>-42333.281366614101</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="31">
         <f>SUM($B$15:H15)</f>
         <v>-16464.375387798962</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="31">
         <f>SUM($B$15:I15)</f>
         <v>4567.2554892865155</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="31">
         <f>SUM($B$15:J15)</f>
         <v>25085.919759613811</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <f>NPV(0.025, C14:J14)</f>
         <v>180085.91975961381</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <v>155000</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="32">
         <f>B17/B18</f>
         <v>1.1618446436104117</v>
       </c>
@@ -3035,151 +3043,151 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="24" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="24"/>
-    <col min="3" max="3" width="22.85546875" style="24" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="12" customWidth="1"/>
-    <col min="5" max="7" width="8.85546875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="12" customWidth="1"/>
-    <col min="9" max="11" width="8.85546875" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="14.140625" style="24"/>
+    <col min="1" max="1" width="12.42578125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="22"/>
+    <col min="3" max="3" width="22.85546875" style="22" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="11" customWidth="1"/>
+    <col min="5" max="7" width="8.85546875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="11" customWidth="1"/>
+    <col min="9" max="11" width="8.85546875" style="11" customWidth="1"/>
+    <col min="12" max="16384" width="14.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="26">
+      <c r="D1" s="24">
         <v>0</v>
       </c>
-      <c r="E1" s="26">
+      <c r="E1" s="24">
         <v>1</v>
       </c>
-      <c r="F1" s="26">
+      <c r="F1" s="24">
         <v>2</v>
       </c>
-      <c r="G1" s="26">
+      <c r="G1" s="24">
         <v>3</v>
       </c>
-      <c r="H1" s="26">
+      <c r="H1" s="24">
         <v>4</v>
       </c>
-      <c r="I1" s="26">
+      <c r="I1" s="24">
         <v>5</v>
       </c>
-      <c r="J1" s="26">
+      <c r="J1" s="24">
         <v>6</v>
       </c>
-      <c r="K1" s="26">
+      <c r="K1" s="24">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="40">
+      <c r="C2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="37">
         <v>-70000</v>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="37">
         <v>5000</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="37">
         <v>7500</v>
       </c>
-      <c r="G2" s="40">
+      <c r="G2" s="37">
         <v>10000</v>
       </c>
-      <c r="H2" s="40">
+      <c r="H2" s="37">
         <v>12500</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="37">
         <v>15000</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="37">
         <v>17500</v>
       </c>
-      <c r="K2" s="40">
+      <c r="K2" s="37">
         <v>20000</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>0</v>
+      <c r="B4" s="15" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="41">
-        <f>NPV(B5,$D$2:$K$2)</f>
-        <v>9430.0811003782946</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="38">
+        <f>$D$2+NPV(B5,$E$2:$K$2)</f>
+        <v>9618.6827223858563</v>
+      </c>
+      <c r="B5" s="11">
         <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="41">
-        <f t="shared" ref="A6:A10" si="0">NPV(B6,$D$2:$K$2)</f>
-        <v>5862.4072112749327</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="38">
+        <f t="shared" ref="A6:A10" si="0">$D$2+NPV(B6,$E$2:$K$2)</f>
+        <v>6038.2794276131899</v>
+      </c>
+      <c r="B6" s="11">
         <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="41">
-        <f t="shared" si="0"/>
-        <v>2571.7759092454239</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="38">
+        <f t="shared" si="0"/>
+        <v>2674.6469456152554</v>
+      </c>
+      <c r="B7" s="11">
         <v>0.04</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="41">
-        <f t="shared" si="0"/>
-        <v>-464.69398921551533</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="38">
+        <f t="shared" si="0"/>
+        <v>-487.92868867628567</v>
+      </c>
+      <c r="B8" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="41">
-        <f t="shared" si="0"/>
-        <v>-3267.790211214663</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="38">
+        <f t="shared" si="0"/>
+        <v>-3463.8576238875539</v>
+      </c>
+      <c r="B9" s="11">
         <v>0.06</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="41">
-        <f t="shared" si="0"/>
-        <v>-5856.41773406621</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="38">
+        <f t="shared" si="0"/>
+        <v>-6266.3669754508446</v>
+      </c>
+      <c r="B10" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fin_math/code/Capital Budgeting.xlsx
+++ b/fin_math/code/Capital Budgeting.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen Fratini\Documents\_Work Related\_My Books\Financial Math with Python\Review\Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen Fratini\Documents\_Work Related\_My Books\Financial Math with Python\CodeForBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C269B11-D5BB-4699-B2E7-8EAC6E242FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E4E2FE-3306-47C9-8680-F936B5D6C6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7350" yWindow="1110" windowWidth="16560" windowHeight="11175" xr2:uid="{EAB1697F-5FC0-4B8A-A2CE-1FD59A4F4BBF}"/>
+    <workbookView xWindow="6225" yWindow="2475" windowWidth="17805" windowHeight="11175" firstSheet="6" activeTab="10" xr2:uid="{EAB1697F-5FC0-4B8A-A2CE-1FD59A4F4BBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Acme Furniture" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="DPP and PI" sheetId="8" r:id="rId8"/>
     <sheet name="Ex 1" sheetId="6" r:id="rId9"/>
     <sheet name="Ex 2" sheetId="10" r:id="rId10"/>
+    <sheet name="Ex 3" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="49">
   <si>
     <t>Rate of Return</t>
   </si>
@@ -181,6 +182,15 @@
   </si>
   <si>
     <t>Semi-annual loan payment</t>
+  </si>
+  <si>
+    <t>Time in years</t>
+  </si>
+  <si>
+    <t>NPV at 2% Cost of Capital</t>
+  </si>
+  <si>
+    <t>Guess at Semi-annual Loan Payment</t>
   </si>
 </sst>
 </file>
@@ -253,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -390,6 +400,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
@@ -1450,6 +1465,236 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A95B1223-0C91-4597-A2BE-43F101A3A8D1}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>0.5</v>
+      </c>
+      <c r="D1">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1.5</v>
+      </c>
+      <c r="F1">
+        <v>2</v>
+      </c>
+      <c r="G1">
+        <v>2.5</v>
+      </c>
+      <c r="H1">
+        <v>3</v>
+      </c>
+      <c r="I1">
+        <v>3.5</v>
+      </c>
+      <c r="J1">
+        <v>4</v>
+      </c>
+      <c r="K1">
+        <v>4.5</v>
+      </c>
+      <c r="L1">
+        <v>5</v>
+      </c>
+      <c r="M1">
+        <v>5.5</v>
+      </c>
+      <c r="N1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="46">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="46">
+        <v>22000</v>
+      </c>
+      <c r="E2" s="46">
+        <v>24000</v>
+      </c>
+      <c r="F2" s="46">
+        <v>26000</v>
+      </c>
+      <c r="G2" s="46">
+        <v>28000</v>
+      </c>
+      <c r="H2" s="46">
+        <v>30000</v>
+      </c>
+      <c r="I2" s="46">
+        <v>32000</v>
+      </c>
+      <c r="J2" s="46">
+        <v>34000</v>
+      </c>
+      <c r="K2" s="46">
+        <v>36000</v>
+      </c>
+      <c r="L2" s="46">
+        <v>38000</v>
+      </c>
+      <c r="M2" s="46">
+        <v>41000</v>
+      </c>
+      <c r="N2" s="46">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="49">
+        <v>-225000</v>
+      </c>
+      <c r="C3" s="50">
+        <f>-$B$7</f>
+        <v>-11158.3</v>
+      </c>
+      <c r="D3" s="50">
+        <f t="shared" ref="D3:L3" si="0">-$B$7</f>
+        <v>-11158.3</v>
+      </c>
+      <c r="E3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="F3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="G3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="H3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="I3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="J3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="K3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="L3" s="50">
+        <f t="shared" si="0"/>
+        <v>-11158.3</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="49">
+        <v>-225000</v>
+      </c>
+      <c r="C4" s="46">
+        <f>SUM(C2:C3)</f>
+        <v>8841.7000000000007</v>
+      </c>
+      <c r="D4" s="46">
+        <f t="shared" ref="D4:N4" si="1">SUM(D2:D3)</f>
+        <v>10841.7</v>
+      </c>
+      <c r="E4" s="46">
+        <f t="shared" si="1"/>
+        <v>12841.7</v>
+      </c>
+      <c r="F4" s="46">
+        <f t="shared" si="1"/>
+        <v>14841.7</v>
+      </c>
+      <c r="G4" s="46">
+        <f t="shared" si="1"/>
+        <v>16841.7</v>
+      </c>
+      <c r="H4" s="46">
+        <f t="shared" si="1"/>
+        <v>18841.7</v>
+      </c>
+      <c r="I4" s="46">
+        <f t="shared" si="1"/>
+        <v>20841.7</v>
+      </c>
+      <c r="J4" s="46">
+        <f t="shared" si="1"/>
+        <v>22841.7</v>
+      </c>
+      <c r="K4" s="46">
+        <f t="shared" si="1"/>
+        <v>24841.7</v>
+      </c>
+      <c r="L4" s="46">
+        <f t="shared" si="1"/>
+        <v>26841.7</v>
+      </c>
+      <c r="M4" s="46">
+        <f t="shared" si="1"/>
+        <v>41000</v>
+      </c>
+      <c r="N4" s="46">
+        <f t="shared" si="1"/>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <f>11158.3</f>
+        <v>11158.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="48">
+        <f>B4+NPV(0.02,C4:N4)</f>
+        <v>6.9271780666895211E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C4 D4:I4 J4:N4" formulaRange="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FB6DFE-50F0-4ACE-8590-6E239BEC3554}">
   <dimension ref="A1:U13"/>
